--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1478"/>
+  <dimension ref="A1:B1479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15210,6 +15210,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1479">
+      <c r="A1479" s="1" t="inlineStr">
+        <is>
+          <t>22 August 2026</t>
+        </is>
+      </c>
+      <c r="B1479" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1479"/>
+  <dimension ref="A1:B1480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15220,6 +15220,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1480">
+      <c r="A1480" s="1" t="inlineStr">
+        <is>
+          <t>23 August 2026</t>
+        </is>
+      </c>
+      <c r="B1480" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1480"/>
+  <dimension ref="A1:B1481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15230,6 +15230,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1481">
+      <c r="A1481" s="1" t="inlineStr">
+        <is>
+          <t>24 August 2026</t>
+        </is>
+      </c>
+      <c r="B1481" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1481"/>
+  <dimension ref="A1:B1482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15240,6 +15240,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1482">
+      <c r="A1482" s="1" t="inlineStr">
+        <is>
+          <t>25 August 2026</t>
+        </is>
+      </c>
+      <c r="B1482" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1482"/>
+  <dimension ref="A1:B1483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15250,6 +15250,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1483">
+      <c r="A1483" s="1" t="inlineStr">
+        <is>
+          <t>26 August 2026</t>
+        </is>
+      </c>
+      <c r="B1483" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1483"/>
+  <dimension ref="A1:B1484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15260,6 +15260,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1484">
+      <c r="A1484" s="1" t="inlineStr">
+        <is>
+          <t>27 August 2026</t>
+        </is>
+      </c>
+      <c r="B1484" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1484"/>
+  <dimension ref="A1:B1485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15270,6 +15270,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1485">
+      <c r="A1485" s="1" t="inlineStr">
+        <is>
+          <t>28 August 2026</t>
+        </is>
+      </c>
+      <c r="B1485" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1485"/>
+  <dimension ref="A1:B1486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15280,6 +15280,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1486">
+      <c r="A1486" s="1" t="inlineStr">
+        <is>
+          <t>29 August 2026</t>
+        </is>
+      </c>
+      <c r="B1486" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1486"/>
+  <dimension ref="A1:B1487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15290,6 +15290,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1487">
+      <c r="A1487" s="1" t="inlineStr">
+        <is>
+          <t>30 August 2026</t>
+        </is>
+      </c>
+      <c r="B1487" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1487"/>
+  <dimension ref="A1:B1488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15300,6 +15300,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1488">
+      <c r="A1488" s="1" t="inlineStr">
+        <is>
+          <t>31 August 2026</t>
+        </is>
+      </c>
+      <c r="B1488" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1488"/>
+  <dimension ref="A1:B1489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15310,6 +15310,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1489">
+      <c r="A1489" s="1" t="inlineStr">
+        <is>
+          <t>01 September 2026</t>
+        </is>
+      </c>
+      <c r="B1489" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1489"/>
+  <dimension ref="A1:B1490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15320,6 +15320,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1490">
+      <c r="A1490" s="1" t="inlineStr">
+        <is>
+          <t>02 September 2026</t>
+        </is>
+      </c>
+      <c r="B1490" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1490"/>
+  <dimension ref="A1:B1491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15330,6 +15330,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1491">
+      <c r="A1491" s="1" t="inlineStr">
+        <is>
+          <t>03 September 2026</t>
+        </is>
+      </c>
+      <c r="B1491" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1491"/>
+  <dimension ref="A1:B1492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15340,6 +15340,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1492">
+      <c r="A1492" s="1" t="inlineStr">
+        <is>
+          <t>04 September 2026</t>
+        </is>
+      </c>
+      <c r="B1492" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1492"/>
+  <dimension ref="A1:B1493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15350,6 +15350,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1493">
+      <c r="A1493" s="1" t="inlineStr">
+        <is>
+          <t>05 September 2026</t>
+        </is>
+      </c>
+      <c r="B1493" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1493"/>
+  <dimension ref="A1:B1494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15360,6 +15360,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1494">
+      <c r="A1494" s="1" t="inlineStr">
+        <is>
+          <t>06 September 2026</t>
+        </is>
+      </c>
+      <c r="B1494" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1494"/>
+  <dimension ref="A1:B1495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15370,6 +15370,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1495">
+      <c r="A1495" s="1" t="inlineStr">
+        <is>
+          <t>07 September 2026</t>
+        </is>
+      </c>
+      <c r="B1495" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1495"/>
+  <dimension ref="A1:B1496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15380,6 +15380,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1496">
+      <c r="A1496" s="1" t="inlineStr">
+        <is>
+          <t>08 September 2026</t>
+        </is>
+      </c>
+      <c r="B1496" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1496"/>
+  <dimension ref="A1:B1497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15390,6 +15390,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1497">
+      <c r="A1497" s="1" t="inlineStr">
+        <is>
+          <t>09 September 2026</t>
+        </is>
+      </c>
+      <c r="B1497" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1497"/>
+  <dimension ref="A1:B1498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15400,6 +15400,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1498">
+      <c r="A1498" s="1" t="inlineStr">
+        <is>
+          <t>10 September 2026</t>
+        </is>
+      </c>
+      <c r="B1498" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1498"/>
+  <dimension ref="A1:B1499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15410,6 +15410,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1499">
+      <c r="A1499" s="1" t="inlineStr">
+        <is>
+          <t>11 September 2026</t>
+        </is>
+      </c>
+      <c r="B1499" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1499"/>
+  <dimension ref="A1:B1500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15420,6 +15420,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1500">
+      <c r="A1500" s="1" t="inlineStr">
+        <is>
+          <t>12 September 2026</t>
+        </is>
+      </c>
+      <c r="B1500" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1500"/>
+  <dimension ref="A1:B1501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15430,6 +15430,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1501">
+      <c r="A1501" s="1" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="B1501" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1501"/>
+  <dimension ref="A1:B1502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15440,6 +15440,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1502">
+      <c r="A1502" s="1" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="B1502" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1502"/>
+  <dimension ref="A1:B1503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15450,6 +15450,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1503">
+      <c r="A1503" s="1" t="inlineStr">
+        <is>
+          <t>15 September 2026</t>
+        </is>
+      </c>
+      <c r="B1503" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1503"/>
+  <dimension ref="A1:B1504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15460,6 +15460,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1504">
+      <c r="A1504" s="1" t="inlineStr">
+        <is>
+          <t>16 September 2026</t>
+        </is>
+      </c>
+      <c r="B1504" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1504"/>
+  <dimension ref="A1:B1505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15470,6 +15470,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1505">
+      <c r="A1505" s="1" t="inlineStr">
+        <is>
+          <t>17 September 2026</t>
+        </is>
+      </c>
+      <c r="B1505" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1505"/>
+  <dimension ref="A1:B1506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15480,6 +15480,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1506">
+      <c r="A1506" s="1" t="inlineStr">
+        <is>
+          <t>18 September 2026</t>
+        </is>
+      </c>
+      <c r="B1506" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1506"/>
+  <dimension ref="A1:B1507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15490,6 +15490,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1507">
+      <c r="A1507" s="1" t="inlineStr">
+        <is>
+          <t>19 September 2026</t>
+        </is>
+      </c>
+      <c r="B1507" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1507"/>
+  <dimension ref="A1:B1508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15500,6 +15500,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1508">
+      <c r="A1508" s="1" t="inlineStr">
+        <is>
+          <t>20 September 2026</t>
+        </is>
+      </c>
+      <c r="B1508" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1508"/>
+  <dimension ref="A1:B1509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15510,6 +15510,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1509">
+      <c r="A1509" s="1" t="inlineStr">
+        <is>
+          <t>21 September 2026</t>
+        </is>
+      </c>
+      <c r="B1509" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1509"/>
+  <dimension ref="A1:B1510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15520,6 +15520,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1510">
+      <c r="A1510" s="1" t="inlineStr">
+        <is>
+          <t>22 September 2026</t>
+        </is>
+      </c>
+      <c r="B1510" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1510"/>
+  <dimension ref="A1:B1511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15530,6 +15530,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1511">
+      <c r="A1511" s="1" t="inlineStr">
+        <is>
+          <t>23 September 2026</t>
+        </is>
+      </c>
+      <c r="B1511" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1511"/>
+  <dimension ref="A1:B1512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15540,6 +15540,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1512">
+      <c r="A1512" s="1" t="inlineStr">
+        <is>
+          <t>24 September 2026</t>
+        </is>
+      </c>
+      <c r="B1512" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1512"/>
+  <dimension ref="A1:B1513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15550,6 +15550,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1513">
+      <c r="A1513" s="1" t="inlineStr">
+        <is>
+          <t>25 September 2026</t>
+        </is>
+      </c>
+      <c r="B1513" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1513"/>
+  <dimension ref="A1:B1514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15560,6 +15560,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1514">
+      <c r="A1514" s="1" t="inlineStr">
+        <is>
+          <t>26 September 2026</t>
+        </is>
+      </c>
+      <c r="B1514" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1514"/>
+  <dimension ref="A1:B1515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15570,6 +15570,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1515">
+      <c r="A1515" s="1" t="inlineStr">
+        <is>
+          <t>27 September 2026</t>
+        </is>
+      </c>
+      <c r="B1515" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1515"/>
+  <dimension ref="A1:B1516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15580,6 +15580,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1516">
+      <c r="A1516" s="1" t="inlineStr">
+        <is>
+          <t>28 September 2026</t>
+        </is>
+      </c>
+      <c r="B1516" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1516"/>
+  <dimension ref="A1:B1517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15590,6 +15590,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1517">
+      <c r="A1517" s="1" t="inlineStr">
+        <is>
+          <t>29 September 2026</t>
+        </is>
+      </c>
+      <c r="B1517" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1517"/>
+  <dimension ref="A1:B1518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15600,6 +15600,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1518">
+      <c r="A1518" s="1" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="B1518" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1518"/>
+  <dimension ref="A1:B1519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15610,6 +15610,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1519">
+      <c r="A1519" s="1" t="inlineStr">
+        <is>
+          <t>01 October 2026</t>
+        </is>
+      </c>
+      <c r="B1519" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1519"/>
+  <dimension ref="A1:B1520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15620,6 +15620,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1520">
+      <c r="A1520" s="1" t="inlineStr">
+        <is>
+          <t>02 October 2026</t>
+        </is>
+      </c>
+      <c r="B1520" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1520"/>
+  <dimension ref="A1:B1521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15630,6 +15630,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1521">
+      <c r="A1521" s="1" t="inlineStr">
+        <is>
+          <t>03 October 2026</t>
+        </is>
+      </c>
+      <c r="B1521" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1521"/>
+  <dimension ref="A1:B1522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15640,6 +15640,16 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1522">
+      <c r="A1522" s="1" t="inlineStr">
+        <is>
+          <t>04 October 2026</t>
+        </is>
+      </c>
+      <c r="B1522" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1522"/>
+  <dimension ref="A1:B1523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15650,6 +15650,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1523">
+      <c r="A1523" s="1" t="inlineStr">
+        <is>
+          <t>05 October 2026</t>
+        </is>
+      </c>
+      <c r="B1523" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1523"/>
+  <dimension ref="A1:B1524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15660,6 +15660,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1524">
+      <c r="A1524" s="1" t="inlineStr">
+        <is>
+          <t>06 October 2026</t>
+        </is>
+      </c>
+      <c r="B1524" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1524"/>
+  <dimension ref="A1:B1525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15670,6 +15670,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1525">
+      <c r="A1525" s="1" t="inlineStr">
+        <is>
+          <t>07 October 2026</t>
+        </is>
+      </c>
+      <c r="B1525" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1525"/>
+  <dimension ref="A1:B1526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15680,6 +15680,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1526">
+      <c r="A1526" s="1" t="inlineStr">
+        <is>
+          <t>08 October 2026</t>
+        </is>
+      </c>
+      <c r="B1526" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1526"/>
+  <dimension ref="A1:B1527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15690,6 +15690,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1527">
+      <c r="A1527" s="1" t="inlineStr">
+        <is>
+          <t>09 October 2026</t>
+        </is>
+      </c>
+      <c r="B1527" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1527"/>
+  <dimension ref="A1:B1528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15700,6 +15700,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1528">
+      <c r="A1528" s="1" t="inlineStr">
+        <is>
+          <t>10 October 2026</t>
+        </is>
+      </c>
+      <c r="B1528" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1528"/>
+  <dimension ref="A1:B1529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15710,6 +15710,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1529">
+      <c r="A1529" s="1" t="inlineStr">
+        <is>
+          <t>11 October 2026</t>
+        </is>
+      </c>
+      <c r="B1529" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1529"/>
+  <dimension ref="A1:B1530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15720,6 +15720,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1530">
+      <c r="A1530" s="1" t="inlineStr">
+        <is>
+          <t>12 October 2026</t>
+        </is>
+      </c>
+      <c r="B1530" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1530"/>
+  <dimension ref="A1:B1531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15730,6 +15730,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1531">
+      <c r="A1531" s="1" t="inlineStr">
+        <is>
+          <t>13 October 2026</t>
+        </is>
+      </c>
+      <c r="B1531" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1531"/>
+  <dimension ref="A1:B1532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15740,6 +15740,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1532">
+      <c r="A1532" s="1" t="inlineStr">
+        <is>
+          <t>14 October 2026</t>
+        </is>
+      </c>
+      <c r="B1532" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1532"/>
+  <dimension ref="A1:B1533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15750,6 +15750,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1533">
+      <c r="A1533" s="1" t="inlineStr">
+        <is>
+          <t>15 October 2026</t>
+        </is>
+      </c>
+      <c r="B1533" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1533"/>
+  <dimension ref="A1:B1534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15760,6 +15760,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1534">
+      <c r="A1534" s="1" t="inlineStr">
+        <is>
+          <t>16 October 2026</t>
+        </is>
+      </c>
+      <c r="B1534" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1534"/>
+  <dimension ref="A1:B1535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15770,6 +15770,16 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1535">
+      <c r="A1535" s="1" t="inlineStr">
+        <is>
+          <t>17 October 2026</t>
+        </is>
+      </c>
+      <c r="B1535" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1535"/>
+  <dimension ref="A1:B1536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15780,6 +15780,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1536">
+      <c r="A1536" s="1" t="inlineStr">
+        <is>
+          <t>18 October 2026</t>
+        </is>
+      </c>
+      <c r="B1536" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1536"/>
+  <dimension ref="A1:B1537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15790,6 +15790,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1537">
+      <c r="A1537" s="1" t="inlineStr">
+        <is>
+          <t>19 October 2026</t>
+        </is>
+      </c>
+      <c r="B1537" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1537"/>
+  <dimension ref="A1:B1538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15800,6 +15800,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1538">
+      <c r="A1538" s="1" t="inlineStr">
+        <is>
+          <t>20 October 2026</t>
+        </is>
+      </c>
+      <c r="B1538" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1538"/>
+  <dimension ref="A1:B1539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15810,6 +15810,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1539">
+      <c r="A1539" s="1" t="inlineStr">
+        <is>
+          <t>21 October 2026</t>
+        </is>
+      </c>
+      <c r="B1539" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1539"/>
+  <dimension ref="A1:B1540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15820,6 +15820,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1540">
+      <c r="A1540" s="1" t="inlineStr">
+        <is>
+          <t>22 October 2026</t>
+        </is>
+      </c>
+      <c r="B1540" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1540"/>
+  <dimension ref="A1:B1541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15830,6 +15830,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1541">
+      <c r="A1541" s="1" t="inlineStr">
+        <is>
+          <t>23 October 2026</t>
+        </is>
+      </c>
+      <c r="B1541" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1541"/>
+  <dimension ref="A1:B1542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15840,6 +15840,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1542">
+      <c r="A1542" s="1" t="inlineStr">
+        <is>
+          <t>24 October 2026</t>
+        </is>
+      </c>
+      <c r="B1542" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1542"/>
+  <dimension ref="A1:B1543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15850,6 +15850,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1543">
+      <c r="A1543" s="1" t="inlineStr">
+        <is>
+          <t>25 October 2026</t>
+        </is>
+      </c>
+      <c r="B1543" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1543"/>
+  <dimension ref="A1:B1544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15860,6 +15860,16 @@
         <v>10</v>
       </c>
     </row>
+    <row r="1544">
+      <c r="A1544" s="1" t="inlineStr">
+        <is>
+          <t>26 October 2026</t>
+        </is>
+      </c>
+      <c r="B1544" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1544"/>
+  <dimension ref="A1:B1545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15870,6 +15870,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1545">
+      <c r="A1545" s="1" t="inlineStr">
+        <is>
+          <t>27 October 2026</t>
+        </is>
+      </c>
+      <c r="B1545" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1545"/>
+  <dimension ref="A1:B1546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15880,6 +15880,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1546">
+      <c r="A1546" s="1" t="inlineStr">
+        <is>
+          <t>28 October 2026</t>
+        </is>
+      </c>
+      <c r="B1546" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1546"/>
+  <dimension ref="A1:B1547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15890,6 +15890,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1547">
+      <c r="A1547" s="1" t="inlineStr">
+        <is>
+          <t>29 October 2026</t>
+        </is>
+      </c>
+      <c r="B1547" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1547"/>
+  <dimension ref="A1:B1548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15900,6 +15900,16 @@
         <v>11</v>
       </c>
     </row>
+    <row r="1548">
+      <c r="A1548" s="1" t="inlineStr">
+        <is>
+          <t>30 October 2026</t>
+        </is>
+      </c>
+      <c r="B1548" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
